--- a/敏捷开发Sprint追踪表.xlsx
+++ b/敏捷开发Sprint追踪表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080" activeTab="3"/>
+    <workbookView windowWidth="22188" windowHeight="9060" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="需求列表" sheetId="5" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="55">
   <si>
     <t>模块</t>
   </si>
@@ -129,7 +129,58 @@
     <t>李四</t>
   </si>
   <si>
-    <t>Sprint1 (2016/0x/xx~2026/0x/xx)</t>
+    <t>Sprint1 (2026/04/08~2026/04/19)</t>
+  </si>
+  <si>
+    <t>项目初始化与技术栈搭建</t>
+  </si>
+  <si>
+    <t>搭建项目基础框架,Django + Vue.js</t>
+  </si>
+  <si>
+    <t>王君悦</t>
+  </si>
+  <si>
+    <t>to do</t>
+  </si>
+  <si>
+    <t>基础项目结构</t>
+  </si>
+  <si>
+    <t>用户注册功能</t>
+  </si>
+  <si>
+    <t>支持学号/邮箱/手机号</t>
+  </si>
+  <si>
+    <t>赵溢</t>
+  </si>
+  <si>
+    <t>能成功注册新用户</t>
+  </si>
+  <si>
+    <t>用户登录功能</t>
+  </si>
+  <si>
+    <t>含记住密码</t>
+  </si>
+  <si>
+    <t>能使用账号密码登录系统</t>
+  </si>
+  <si>
+    <t>修改资料、密码</t>
+  </si>
+  <si>
+    <t>能修改个人资料和密码</t>
+  </si>
+  <si>
+    <t>权限管理系统</t>
+  </si>
+  <si>
+    <t>管理员/普通用户角色</t>
+  </si>
+  <si>
+    <t>管理员和普通用户权限分离</t>
   </si>
   <si>
     <t>做得好的</t>
@@ -157,7 +208,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -192,13 +243,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -343,7 +387,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -401,12 +445,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -658,148 +696,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1188,10 +1226,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="2"/>
   <cols>
-    <col min="2" max="2" width="23.0636363636364" customWidth="1"/>
-    <col min="3" max="3" width="41.8636363636364" customWidth="1"/>
+    <col min="2" max="2" width="23.0648148148148" customWidth="1"/>
+    <col min="3" max="3" width="41.8611111111111" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1270,13 +1308,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="59.5272727272727" customWidth="1"/>
+    <col min="1" max="1" width="59.5277777777778" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="23.8636363636364" customWidth="1"/>
+    <col min="3" max="3" width="23.8611111111111" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="28.9272727272727" customWidth="1"/>
+    <col min="5" max="5" width="28.9259259259259" customWidth="1"/>
     <col min="6" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1324,13 +1362,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="3" width="26.7272727272727" customWidth="1"/>
+    <col min="2" max="3" width="26.7314814814815" customWidth="1"/>
     <col min="4" max="4" width="17" customWidth="1"/>
     <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="26.8" customWidth="1"/>
+    <col min="6" max="6" width="26.7962962962963" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1407,11 +1445,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="5"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="24.1363636363636" customWidth="1"/>
+    <col min="1" max="1" width="24.8888888888889" customWidth="1"/>
+    <col min="2" max="2" width="32.8888888888889" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="27.1111111111111" customWidth="1"/>
     <col min="5" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1443,6 +1483,106 @@
       </c>
       <c r="F2" s="1" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +1598,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="5" width="22" customWidth="1"/>
   </cols>
@@ -1468,13 +1608,13 @@
         <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>26</v>
@@ -1482,7 +1622,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="2" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1493,7 +1633,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="2" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:1">

--- a/敏捷开发Sprint追踪表.xlsx
+++ b/敏捷开发Sprint追踪表.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="68">
   <si>
     <t>模块</t>
   </si>
@@ -141,46 +141,85 @@
     <t>王君悦</t>
   </si>
   <si>
+    <t>done</t>
+  </si>
+  <si>
+    <t>基础项目结构</t>
+  </si>
+  <si>
+    <t>用户注册功能</t>
+  </si>
+  <si>
+    <t>支持学号/邮箱/手机号</t>
+  </si>
+  <si>
+    <t>赵溢</t>
+  </si>
+  <si>
+    <t>能成功注册新用户</t>
+  </si>
+  <si>
+    <t>用户登录功能</t>
+  </si>
+  <si>
+    <t>含记住密码</t>
+  </si>
+  <si>
+    <t>能使用账号密码登录系统</t>
+  </si>
+  <si>
+    <t>修改资料、密码</t>
+  </si>
+  <si>
+    <t>能修改个人资料和密码</t>
+  </si>
+  <si>
+    <t>权限管理系统</t>
+  </si>
+  <si>
+    <t>管理员/普通用户角色</t>
+  </si>
+  <si>
+    <t>管理员和普通用户权限分离</t>
+  </si>
+  <si>
+    <t>Sprint2 (2026/04/21~2026/05/03)</t>
+  </si>
+  <si>
+    <t>活动发布功能</t>
+  </si>
+  <si>
+    <t>标题、时间、类型、地点、描述、图片</t>
+  </si>
+  <si>
     <t>to do</t>
   </si>
   <si>
-    <t>基础项目结构</t>
-  </si>
-  <si>
-    <t>用户注册功能</t>
-  </si>
-  <si>
-    <t>支持学号/邮箱/手机号</t>
-  </si>
-  <si>
-    <t>赵溢</t>
-  </si>
-  <si>
-    <t>能成功注册新用户</t>
-  </si>
-  <si>
-    <t>用户登录功能</t>
-  </si>
-  <si>
-    <t>含记住密码</t>
-  </si>
-  <si>
-    <t>能使用账号密码登录系统</t>
-  </si>
-  <si>
-    <t>修改资料、密码</t>
-  </si>
-  <si>
-    <t>能修改个人资料和密码</t>
-  </si>
-  <si>
-    <t>权限管理系统</t>
-  </si>
-  <si>
-    <t>管理员/普通用户角色</t>
-  </si>
-  <si>
-    <t>管理员和普通用户权限分离</t>
+    <t xml:space="preserve"> 管理员能成功发布活动</t>
+  </si>
+  <si>
+    <t>活动编辑和删除功能</t>
+  </si>
+  <si>
+    <t>管理员能编辑和删除已发布活动</t>
+  </si>
+  <si>
+    <t>活动列表页面</t>
+  </si>
+  <si>
+    <t>支持按时间、类型筛选</t>
+  </si>
+  <si>
+    <t>活动列表能正确展示所有活动</t>
+  </si>
+  <si>
+    <t>活动详情页面</t>
+  </si>
+  <si>
+    <t>展示活动信息</t>
+  </si>
+  <si>
+    <t>活动详情页能展示完整的活动信息</t>
   </si>
   <si>
     <t>做得好的</t>
@@ -1445,8 +1484,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="5"/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="24.8888888888889" customWidth="1"/>
     <col min="2" max="2" width="32.8888888888889" customWidth="1"/>
@@ -1585,9 +1624,117 @@
         <v>49</v>
       </c>
     </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" t="s">
+        <v>62</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1608,13 +1755,13 @@
         <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>26</v>
@@ -1622,7 +1769,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="2" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1633,7 +1780,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="2" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:1">

--- a/敏捷开发Sprint追踪表.xlsx
+++ b/敏捷开发Sprint追踪表.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="81">
   <si>
     <t>模块</t>
   </si>
@@ -220,6 +220,45 @@
   </si>
   <si>
     <t>活动详情页能展示完整的活动信息</t>
+  </si>
+  <si>
+    <t>Sprint3 (2026/05/6~2026/05/14)</t>
+  </si>
+  <si>
+    <t>活动报名功能</t>
+  </si>
+  <si>
+    <t>普通用户能成功报名活动</t>
+  </si>
+  <si>
+    <t>取消报名功能</t>
+  </si>
+  <si>
+    <t>普通用户能取消已报名活动</t>
+  </si>
+  <si>
+    <t>报名信息查看</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 管理员能查看活动报名人数和名单</t>
+  </si>
+  <si>
+    <t>个人报名记录</t>
+  </si>
+  <si>
+    <t>普通用户能查看个人报名记录</t>
+  </si>
+  <si>
+    <t>活动收藏/取消收藏功能</t>
+  </si>
+  <si>
+    <t>普通用户能收藏和取消收藏活动</t>
+  </si>
+  <si>
+    <t>收藏列表</t>
+  </si>
+  <si>
+    <t>普通用户能查看收藏列表</t>
   </si>
   <si>
     <t>做得好的</t>
@@ -1484,7 +1523,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="24.8888888888889" customWidth="1"/>
@@ -1731,10 +1770,143 @@
         <v>62</v>
       </c>
     </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21" t="s">
+        <v>53</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A14:F14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1755,13 +1927,13 @@
         <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>26</v>
@@ -1769,7 +1941,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -1780,7 +1952,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="2" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:1">

--- a/敏捷开发Sprint追踪表.xlsx
+++ b/敏捷开发Sprint追踪表.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Subject\PBLsax\-SchoolActPlatform\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5CB7841-7C54-499C-9A7F-A99FE123BCA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37647CB9-30CE-4E17-9476-3A3529FD4066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="470" yWindow="0" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="需求列表" sheetId="5" r:id="rId1"/>
     <sheet name="用户故事" sheetId="1" r:id="rId2"/>
-    <sheet name="Sprint1迭代计划" sheetId="2" r:id="rId3"/>
-    <sheet name="SprintN迭代计划 " sheetId="6" r:id="rId4"/>
-    <sheet name="迭代回顾" sheetId="4" r:id="rId5"/>
+    <sheet name="Sprint1~4迭代计划 " sheetId="6" r:id="rId3"/>
+    <sheet name="迭代回顾" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="128">
   <si>
     <t>模块</t>
   </si>
@@ -61,27 +60,15 @@
     <t>活动管理</t>
   </si>
   <si>
-    <t>发布活动、编辑活动、删除活动。</t>
-  </si>
-  <si>
     <t>活动报名</t>
   </si>
   <si>
-    <t>用户报名活动、查看报名信息。</t>
-  </si>
-  <si>
     <t>评论互动</t>
   </si>
   <si>
-    <t>用户评论活动。</t>
-  </si>
-  <si>
     <t>收藏</t>
   </si>
   <si>
-    <t>收藏感兴趣的活动。</t>
-  </si>
-  <si>
     <t>用户故事</t>
   </si>
   <si>
@@ -106,9 +93,6 @@
     <t>P0</t>
   </si>
   <si>
-    <t>Sprint1 (2016/03/24~2026/04/7)</t>
-  </si>
-  <si>
     <t>任务</t>
   </si>
   <si>
@@ -118,21 +102,6 @@
     <t>负责人</t>
   </si>
   <si>
-    <t>Sprint1</t>
-  </si>
-  <si>
-    <t>用户注册开发</t>
-  </si>
-  <si>
-    <t>张三</t>
-  </si>
-  <si>
-    <t>用户注册测试</t>
-  </si>
-  <si>
-    <t>李四</t>
-  </si>
-  <si>
     <t>Sprint1 (2026/04/08~2026/04/19)</t>
   </si>
   <si>
@@ -161,252 +130,360 @@
   </si>
   <si>
     <t>任务</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>评论后端API与展示</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>评论管理功能</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>系统性能优化</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>响应式设计优化</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>全系统集成测试与修复</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>王君悦</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>赵溢</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>王君悦，赵溢</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>TODO</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>发布评论、活动详情页展示评论列表，接口联调</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>管理员可删除不当评论，与API统一设计</t>
   </si>
   <si>
     <t>添加缓存、优化数据库查询，页面加载 ≤2秒</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>适配PC与移动端，操作流畅、布局完整</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>端到端回归测试，覆盖所有用户故事
 修复遗留缺陷
 准备上线检查清单</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>作为普通用户，我要能对活动发表评论，以便表达想法、与他人互动。</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>作为管理员，我要能管理评论，以便维护友善的讨论环境。</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>作为所有用户，我要系统响应快、界面适配多终端，以便流畅使用。</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>作为用户，我要能报名、收藏活动，以便参与并管理我感兴趣的内容。</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>作为管理员，我要能查看报名信息，以便组织活动。</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>活动报名功能</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>取消报名功能</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>报名信息与记录查看</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>活动收藏/取消收藏</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>收藏列表</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Sprint内测试与修复</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Sprint3 (2026/05/06~2026/05/19)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>普通用户报名</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>普通用户取消报名</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>管理员看名单/用户看自己的记录，通过接口权限区</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>普通用户收藏/取消</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>用户查看个人收藏</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>报名、取消、收藏流程联调
 数据一致性验证
 制定Sprint4交互优化清单</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>活动发布功能</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>活动图片上传</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>活动编辑和删除功能</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>活动列表页面</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>活动详情页面</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve"> 图片上传</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>处理存储、压缩、展示</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>管理员可编辑/删除已发布活动</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">含按时间、类型筛选 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>展示完整活动信息</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>活动CRUD全流程测试
 筛选功能、图片上传验证</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>作为管理员，我要能创建、编辑活动，以便通知学生。</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>作为用户，我要能浏览、筛选并查看活动详情，以便了解校园动态。</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>项目初始化与技术栈搭建</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>用户注册功能</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>用户登录功能</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>个人信息管理</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>权限管理系统</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Done</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Django + Vue.js基础框架，可运行</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>支持学号/邮箱/手机号注册</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>含“记住密码”功能</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>可修改个人资料和密码</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>关键依赖项，管理员/普通用户权限分离</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>注册、登录、权限联调
 确保无重大缺陷</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>Sprint4 (2026/05/20~2026/06/02)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>作为用户，我要能注册、登录并管理个人信息，以便安全使用平台。</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>作为管理员，我要拥有分离的权限，以便管理平台。</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>新用户填写用户名、密码、学号、手机号、邮箱完成注册，密码需二次确认。</t>
+  </si>
+  <si>
+    <t>已注册用户通过用户名和密码登录，后端返回 JWT token，前端存储用于后续请求鉴权。</t>
+  </si>
+  <si>
+    <t>用户可查看/修改个人资料（手机号、邮箱、密码），管理员可查看所有用户信息。</t>
+  </si>
+  <si>
+    <t>发布活动</t>
+  </si>
+  <si>
+    <t>管理员填写活动标题、描述、起止时间、类型、地点、主办方后创建活动。</t>
+  </si>
+  <si>
+    <t>编辑活动</t>
+  </si>
+  <si>
+    <t>管理员可修改已发布活动的任意字段，活动状态随之更新。</t>
+  </si>
+  <si>
+    <t>删除活动</t>
+  </si>
+  <si>
+    <t>管理员可删除活动，同时关联的报名记录、收藏、评论应一并清除（或软删除）。</t>
+  </si>
+  <si>
+    <t>用户报名活动</t>
+  </si>
+  <si>
+    <t>普通用户对单个活动进行报名，系统校验活动是否已满、是否已报名，报名后状态为“待确认”。</t>
+  </si>
+  <si>
+    <t>查看报名信息</t>
+  </si>
+  <si>
+    <t>普通用户查看自己的报名记录（列表、状态）；管理员查看某活动的所有报名名单，并支持确认/取消。</t>
+  </si>
+  <si>
+    <t>用户评论活动</t>
+  </si>
+  <si>
+    <t>登录用户在活动详情页发表评论，内容不能为空，按时间倒序展示。管理员可删除任何不当评论。</t>
+  </si>
+  <si>
+    <t>收藏感兴趣的活动</t>
+  </si>
+  <si>
+    <t>登录用户可收藏/取消收藏活动，在个人中心查看收藏列表，点击跳转活动详情。</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>作为一个用户，我需要登录系统以便访问个人相关功能</t>
+  </si>
+  <si>
+    <t>作为一个用户，我希望查看和编辑我的个人信息（手机、邮箱、密码）</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>作为一个管理员，我需要发布活动，以便向用户宣传</t>
+  </si>
+  <si>
+    <t>作为一个管理员，我需要编辑和删除已发布的活动，以便修正错误或取消活动</t>
+  </si>
+  <si>
+    <t>作为一个普通用户，我要能报名活动，以便参与我感兴趣的内容</t>
+  </si>
+  <si>
+    <t>Sprint 3</t>
+  </si>
+  <si>
+    <t>作为一个普通用户，我要能取消报名，以便管理我的日程</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>作为一个普通用户，我要能查看我自己的报名记录，以便追踪参与情况</t>
+  </si>
+  <si>
+    <t>作为一个管理员，我要能查看活动的报名名单，以便组织活动</t>
+  </si>
+  <si>
+    <t>作为一个普通用户，我要能收藏/取消收藏活动，以便保存感兴趣的内容</t>
+  </si>
+  <si>
+    <t>作为一个普通用户，我要能查看我的收藏列表，以便快速找到喜欢的活动</t>
+  </si>
+  <si>
+    <t>作为一个普通用户，我要能对活动发表评论，以便表达想法、与他人互动</t>
+  </si>
+  <si>
+    <t>Sprint 4</t>
+  </si>
+  <si>
+    <t>On going（后端+前端进行中）</t>
+  </si>
+  <si>
+    <t>作为一个管理员，我要能删除不当评论，以便维护友善的讨论环境</t>
+  </si>
+  <si>
+    <t>On going（与评论API统一设计）</t>
   </si>
 </sst>
 </file>
@@ -442,12 +519,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
@@ -478,8 +549,14 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -498,6 +575,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -511,7 +594,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -519,11 +602,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -531,18 +618,23 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -861,131 +953,392 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.08984375" customWidth="1"/>
-    <col min="3" max="3" width="41.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.6328125" customWidth="1"/>
+    <col min="2" max="2" width="20.7265625" customWidth="1"/>
+    <col min="3" max="3" width="98" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="11" t="s">
         <v>4</v>
       </c>
+      <c r="C2" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="7"/>
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="14"/>
+      <c r="B3" s="11" t="s">
         <v>5</v>
       </c>
+      <c r="C3" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="14"/>
+      <c r="B4" s="11" t="s">
         <v>6</v>
       </c>
+      <c r="C4" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="14"/>
+      <c r="B6" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="14"/>
+      <c r="B7" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B8" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="14"/>
+      <c r="B9" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B10" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>14</v>
+      <c r="B11" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A8:A9"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="59.54296875" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="23.81640625" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="28.90625" customWidth="1"/>
+    <col min="1" max="1" width="53" customWidth="1"/>
+    <col min="2" max="2" width="5.54296875" customWidth="1"/>
+    <col min="3" max="3" width="7.453125" customWidth="1"/>
+    <col min="4" max="4" width="9.54296875" customWidth="1"/>
+    <col min="5" max="5" width="23.81640625" customWidth="1"/>
     <col min="6" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="B2" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2">
+      <c r="C2" s="13">
         <v>10</v>
       </c>
+      <c r="D2" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="13">
+        <v>8</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4" s="13">
+        <v>6</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="13">
+        <v>12</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="C6" s="13">
+        <v>8</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="C7" s="13">
+        <v>10</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8" s="13">
+        <v>6</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C9" s="13">
+        <v>6</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="C10" s="13">
+        <v>8</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C11" s="13">
+        <v>6</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" s="13">
+        <v>4</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C13" s="13">
+        <v>12</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" s="13">
+        <v>4</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>127</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -994,89 +1347,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="3" width="26.7265625" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="26.81640625" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B1" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B1:G1"/>
-  </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
@@ -1091,541 +1361,541 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
+      <c r="A1" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>87</v>
+      <c r="A3" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="C3">
         <v>3</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>93</v>
+      <c r="D3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>88</v>
+      <c r="A4" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>78</v>
       </c>
       <c r="C4">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>94</v>
+        <v>24</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B5" s="9" t="s">
-        <v>89</v>
+      <c r="B5" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>95</v>
+        <v>24</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="9" t="s">
-        <v>90</v>
+      <c r="B6" s="4" t="s">
+        <v>80</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>96</v>
+        <v>24</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="9" t="s">
-        <v>91</v>
+      <c r="B7" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
-      <c r="D7" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>97</v>
+      <c r="D7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="B8" s="9" t="s">
-        <v>66</v>
+      <c r="B8" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
-      <c r="D8" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>98</v>
+      <c r="D8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
+      <c r="A15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="F16" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>74</v>
+      <c r="A17" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="C17">
         <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>33</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>79</v>
+        <v>23</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>75</v>
+      <c r="A18" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>65</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>80</v>
+      <c r="D18" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B19" s="9" t="s">
-        <v>76</v>
+      <c r="B19" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="C19">
         <v>3</v>
       </c>
-      <c r="D19" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>81</v>
+      <c r="D19" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B20" s="9" t="s">
-        <v>77</v>
+      <c r="B20" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="C20">
         <v>3</v>
       </c>
       <c r="D20" t="s">
-        <v>34</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>82</v>
+        <v>24</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B21" s="9" t="s">
-        <v>78</v>
+      <c r="B21" s="4" t="s">
+        <v>68</v>
       </c>
       <c r="C21">
         <v>3</v>
       </c>
-      <c r="D21" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>83</v>
+      <c r="D21" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="28" x14ac:dyDescent="0.25">
-      <c r="B22" s="9" t="s">
-        <v>66</v>
+      <c r="B22" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
-      <c r="D22" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>84</v>
+      <c r="D22" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
+      <c r="A27" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="F28" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>61</v>
+      <c r="A29" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>51</v>
       </c>
       <c r="C29">
         <v>1</v>
       </c>
-      <c r="D29" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E29" s="9" t="s">
+      <c r="D29" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F29" s="9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>62</v>
+      <c r="B30" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="C30">
         <v>1</v>
       </c>
       <c r="D30" t="s">
-        <v>33</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>69</v>
+        <v>23</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B31" s="9" t="s">
-        <v>63</v>
+      <c r="B31" s="4" t="s">
+        <v>53</v>
       </c>
       <c r="C31">
         <v>1</v>
       </c>
       <c r="D31" t="s">
-        <v>33</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>70</v>
+        <v>23</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B32" s="9" t="s">
-        <v>64</v>
+      <c r="B32" s="4" t="s">
+        <v>54</v>
       </c>
       <c r="C32">
         <v>1</v>
       </c>
       <c r="D32" t="s">
-        <v>34</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>71</v>
+        <v>24</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="9" t="s">
-        <v>65</v>
+      <c r="B33" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="C33">
         <v>1</v>
       </c>
       <c r="D33" t="s">
-        <v>34</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>72</v>
+        <v>24</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="42" x14ac:dyDescent="0.25">
-      <c r="B34" s="9" t="s">
-        <v>66</v>
+      <c r="B34" s="4" t="s">
+        <v>56</v>
       </c>
       <c r="C34">
         <v>1</v>
       </c>
-      <c r="D34" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F34" s="11" t="s">
-        <v>73</v>
+      <c r="D34" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
+      <c r="A35" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="F36" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>42</v>
+      <c r="A37" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="C37">
         <v>3</v>
       </c>
-      <c r="D37" s="9" t="s">
+      <c r="D37" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E37" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>43</v>
+      <c r="B38" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="C38">
         <v>1</v>
       </c>
-      <c r="D38" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>50</v>
+      <c r="D38" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="F38" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>44</v>
+      <c r="A39" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="C39">
         <v>2</v>
       </c>
-      <c r="D39" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>53</v>
+      <c r="D39" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B40" s="9" t="s">
-        <v>45</v>
+      <c r="B40" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="C40">
         <v>2</v>
       </c>
-      <c r="D40" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E40" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>54</v>
+      <c r="D40" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="42" x14ac:dyDescent="0.25">
-      <c r="B41" s="9" t="s">
-        <v>46</v>
+      <c r="B41" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="C41">
         <v>2</v>
       </c>
-      <c r="D41" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="E41" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F41" s="11" t="s">
-        <v>55</v>
+      <c r="D41" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1635,12 +1905,12 @@
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="A35:F35"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
@@ -1650,52 +1920,52 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>39</v>
+      <c r="A2" s="10" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="7"/>
+      <c r="A3" s="10"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
+      <c r="A4" s="10"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>40</v>
+      <c r="A5" s="10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="7"/>
+      <c r="A6" s="10"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="7"/>
+      <c r="A7" s="10"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="7"/>
+      <c r="A8" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A5:A8"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/敏捷开发Sprint追踪表.xlsx
+++ b/敏捷开发Sprint追踪表.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Subject\PBLsax\-SchoolActPlatform\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ABA1A4D-31D4-4A06-ACFA-E3AC16A2DDCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060" activeTab="2"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="需求列表" sheetId="5" r:id="rId1"/>
@@ -21,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -30,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="145">
   <si>
     <t>模块</t>
   </si>
@@ -401,86 +405,85 @@
     <t>Sprint5(2026/6/03~2026/06/17)</t>
   </si>
   <si>
+    <t>活动编辑功能修复</t>
+  </si>
+  <si>
+    <t>检查权限配置和视图逻辑</t>
+  </si>
+  <si>
+    <t>活动删除功能修复</t>
+  </si>
+  <si>
+    <t>活动海报显示修复</t>
+  </si>
+  <si>
+    <t>检查图片URL配置和静态文件服务</t>
+  </si>
+  <si>
+    <t>普通用户，我要能收藏活动，以便快速找到感兴趣的活动</t>
+  </si>
+  <si>
+    <t>收藏活动功能修复</t>
+  </si>
+  <si>
+    <t>检查收藏接口和权限配置</t>
+  </si>
+  <si>
+    <t>普通用户，我要能对活动发表评论，以便表达想法</t>
+  </si>
+  <si>
+    <t>评论功能修复</t>
+  </si>
+  <si>
+    <t>检查评论接口认证和参数校验</t>
+  </si>
+  <si>
+    <t>普通用户，我要能报名参加活动，以便参与感兴趣的活动</t>
+  </si>
+  <si>
+    <t>报名活动功能修复</t>
+  </si>
+  <si>
+    <t>检查报名接口和活动状态校验</t>
+  </si>
+  <si>
+    <t>功能回归测试</t>
+  </si>
+  <si>
+    <t>覆盖所有用户故事，准备上线检查清单</t>
+  </si>
+  <si>
+    <t>修复第一个bug</t>
+  </si>
+  <si>
+    <t>解决两台电脑两个数据库存储的问题</t>
+  </si>
+  <si>
+    <t>实现两台电脑使用同一账号密码的功能</t>
+  </si>
+  <si>
+    <t>做得好的</t>
+  </si>
+  <si>
+    <t>需要改进</t>
+  </si>
+  <si>
+    <t>行动项</t>
+  </si>
+  <si>
     <t>管理员，我要能管理活动，以便维护活动信息</t>
-  </si>
-  <si>
-    <t>活动编辑功能修复</t>
-  </si>
-  <si>
-    <t>检查权限配置和视图逻辑</t>
-  </si>
-  <si>
-    <t>活动删除功能修复</t>
-  </si>
-  <si>
-    <t>活动海报显示修复</t>
-  </si>
-  <si>
-    <t>检查图片URL配置和静态文件服务</t>
-  </si>
-  <si>
-    <t>普通用户，我要能收藏活动，以便快速找到感兴趣的活动</t>
-  </si>
-  <si>
-    <t>收藏活动功能修复</t>
-  </si>
-  <si>
-    <t>检查收藏接口和权限配置</t>
-  </si>
-  <si>
-    <t>普通用户，我要能对活动发表评论，以便表达想法</t>
-  </si>
-  <si>
-    <t>评论功能修复</t>
-  </si>
-  <si>
-    <t>检查评论接口认证和参数校验</t>
-  </si>
-  <si>
-    <t>普通用户，我要能报名参加活动，以便参与感兴趣的活动</t>
-  </si>
-  <si>
-    <t>报名活动功能修复</t>
-  </si>
-  <si>
-    <t>检查报名接口和活动状态校验</t>
-  </si>
-  <si>
-    <t>功能回归测试</t>
-  </si>
-  <si>
-    <t>覆盖所有用户故事，准备上线检查清单</t>
-  </si>
-  <si>
-    <t>修复第一个bug</t>
-  </si>
-  <si>
-    <t>解决两台电脑两个数据库存储的问题</t>
-  </si>
-  <si>
-    <t>实现两台电脑使用同一账号密码的功能</t>
-  </si>
-  <si>
-    <t>做得好的</t>
-  </si>
-  <si>
-    <t>需要改进</t>
-  </si>
-  <si>
-    <t>行动项</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>done</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="27">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -505,27 +508,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="黑体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -533,154 +515,25 @@
       <sz val="8"/>
       <color rgb="FF0F1115"/>
       <name val="Segoe UI"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -705,194 +558,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -900,283 +567,25 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1185,77 +594,50 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="表2" displayName="表2" ref="A1:F22" totalsRowShown="0">
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F22" etc:filterBottomFollowUsedRange="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表2" displayName="表2" ref="A1:F22" totalsRowShown="0">
+  <autoFilter ref="A1:F22" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="6">
-    <tableColumn id="2" name="用户故事"/>
-    <tableColumn id="4" name="优先级(P0-P5)"/>
-    <tableColumn id="5" name="工作量(小时)"/>
-    <tableColumn id="1" name="迭代周期"/>
-    <tableColumn id="7" name="状态(TODO/On going/Done)"/>
-    <tableColumn id="6" name="备注"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="用户故事"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="优先级(P0-P5)"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="工作量(小时)"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="迭代周期"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="状态(TODO/On going/Done)"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="备注"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1540,125 +922,125 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.6296296296296" customWidth="1"/>
-    <col min="2" max="2" width="20.7222222222222" customWidth="1"/>
+    <col min="1" max="1" width="24.6328125" customWidth="1"/>
+    <col min="2" max="2" width="20.7265625" customWidth="1"/>
     <col min="3" max="3" width="98" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="13" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="7" t="s">
         <v>4</v>
       </c>
       <c r="C2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="9"/>
+      <c r="B3" s="7" t="s">
         <v>6</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="9"/>
+      <c r="B4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="9"/>
+      <c r="B6" s="7" t="s">
         <v>13</v>
       </c>
       <c r="C6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="9"/>
+      <c r="B7" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="13" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="7" t="s">
         <v>18</v>
       </c>
       <c r="C8" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="9"/>
+      <c r="B9" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="13" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="7" t="s">
         <v>23</v>
       </c>
       <c r="C10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="13" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="7" t="s">
         <v>26</v>
       </c>
       <c r="C11" t="s">
@@ -1671,269 +1053,268 @@
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="A8:A9"/>
   </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="53" customWidth="1"/>
-    <col min="2" max="2" width="5.5462962962963" customWidth="1"/>
-    <col min="3" max="3" width="7.4537037037037" customWidth="1"/>
-    <col min="4" max="4" width="9.5462962962963" customWidth="1"/>
-    <col min="5" max="5" width="23.8148148148148" customWidth="1"/>
+    <col min="2" max="2" width="20.08984375" customWidth="1"/>
+    <col min="3" max="3" width="19.6328125" customWidth="1"/>
+    <col min="4" max="4" width="26.90625" customWidth="1"/>
+    <col min="5" max="5" width="23.81640625" customWidth="1"/>
     <col min="6" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="5">
         <v>10</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="10" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="5">
         <v>8</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="10" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="5">
         <v>6</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="10" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="5">
         <v>12</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="10" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="5">
         <v>8</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="10" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="5">
         <v>10</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="10" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="5">
         <v>6</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="10" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="5">
         <v>6</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="10" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="5">
         <v>8</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="10" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="5">
         <v>6</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="10" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="5">
         <v>4</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="10" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="5">
         <v>12</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="10" t="s">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="5">
         <v>4</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="4" t="s">
         <v>56</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
@@ -1941,35 +1322,34 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F51"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="62.9074074074074" customWidth="1"/>
-    <col min="2" max="2" width="32.9074074074074" customWidth="1"/>
+    <col min="1" max="1" width="62.90625" customWidth="1"/>
+    <col min="2" max="2" width="32.90625" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="27.0925925925926" customWidth="1"/>
+    <col min="4" max="4" width="27.08984375" customWidth="1"/>
     <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="52.1759259259259" customWidth="1"/>
+    <col min="6" max="6" width="52.1796875" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="1" t="s">
         <v>58</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -1985,31 +1365,31 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" t="s">
         <v>62</v>
       </c>
       <c r="C3">
         <v>3</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" t="s">
         <v>63</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" t="s">
         <v>66</v>
       </c>
       <c r="C4">
@@ -2018,15 +1398,15 @@
       <c r="D4" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="2:6">
-      <c r="B5" s="6" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
         <v>69</v>
       </c>
       <c r="C5">
@@ -2035,15 +1415,15 @@
       <c r="D5" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="2:6">
-      <c r="B6" s="6" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
         <v>8</v>
       </c>
       <c r="C6">
@@ -2052,58 +1432,58 @@
       <c r="D6" t="s">
         <v>67</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="2:6">
-      <c r="B7" s="6" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
         <v>72</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" t="s">
         <v>63</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="8" ht="28.8" spans="2:6">
-      <c r="B8" s="6" t="s">
+    <row r="8" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
         <v>74</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" t="s">
         <v>75</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>28</v>
       </c>
@@ -2123,11 +1503,11 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="6" t="s">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>78</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" t="s">
         <v>79</v>
       </c>
       <c r="C17">
@@ -2136,52 +1516,52 @@
       <c r="D17" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" t="s">
         <v>80</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="6" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>82</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" t="s">
         <v>83</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" t="s">
         <v>63</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" t="s">
         <v>80</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="2:6">
-      <c r="B19" s="6" t="s">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
         <v>85</v>
       </c>
       <c r="C19">
         <v>3</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" t="s">
         <v>67</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" t="s">
         <v>80</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="20" spans="2:6">
-      <c r="B20" s="6" t="s">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
         <v>87</v>
       </c>
       <c r="C20">
@@ -2190,58 +1570,58 @@
       <c r="D20" t="s">
         <v>67</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" t="s">
         <v>80</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="2:6">
-      <c r="B21" s="6" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
         <v>89</v>
       </c>
       <c r="C21">
         <v>3</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" t="s">
         <v>63</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" t="s">
         <v>80</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F21" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="22" ht="28.8" spans="2:6">
-      <c r="B22" s="6" t="s">
+    <row r="22" spans="1:6" ht="28" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
         <v>74</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" t="s">
         <v>75</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" t="s">
         <v>80</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="8" t="s">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-    </row>
-    <row r="28" spans="1:6">
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>28</v>
       </c>
@@ -2261,31 +1641,31 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="6" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>93</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" t="s">
         <v>94</v>
       </c>
       <c r="C29">
         <v>1</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" t="s">
         <v>63</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" t="s">
         <v>80</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="F29" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="6" t="s">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>96</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" t="s">
         <v>97</v>
       </c>
       <c r="C30">
@@ -2294,15 +1674,15 @@
       <c r="D30" t="s">
         <v>63</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" t="s">
         <v>80</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F30" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="31" spans="2:6">
-      <c r="B31" s="6" t="s">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
         <v>99</v>
       </c>
       <c r="C31">
@@ -2311,15 +1691,15 @@
       <c r="D31" t="s">
         <v>63</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" t="s">
         <v>80</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="F31" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="2:6">
-      <c r="B32" s="6" t="s">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
         <v>101</v>
       </c>
       <c r="C32">
@@ -2328,15 +1708,15 @@
       <c r="D32" t="s">
         <v>67</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E32" t="s">
         <v>80</v>
       </c>
-      <c r="F32" s="6" t="s">
+      <c r="F32" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="33" spans="2:6">
-      <c r="B33" s="6" t="s">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
         <v>103</v>
       </c>
       <c r="C33">
@@ -2345,41 +1725,41 @@
       <c r="D33" t="s">
         <v>67</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="E33" t="s">
         <v>80</v>
       </c>
-      <c r="F33" s="6" t="s">
+      <c r="F33" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="34" ht="43.2" spans="2:6">
-      <c r="B34" s="6" t="s">
+    <row r="34" spans="1:6" ht="42" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
         <v>74</v>
       </c>
       <c r="C34">
         <v>1</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="D34" t="s">
         <v>75</v>
       </c>
-      <c r="E34" s="6" t="s">
+      <c r="E34" t="s">
         <v>80</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F34" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="8" t="s">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-    </row>
-    <row r="36" spans="1:6">
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>28</v>
       </c>
@@ -2399,111 +1779,111 @@
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="6" t="s">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
         <v>107</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" t="s">
         <v>108</v>
       </c>
       <c r="C37">
         <v>3</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="D37" t="s">
         <v>63</v>
       </c>
-      <c r="E37" s="6" t="s">
+      <c r="E37" t="s">
         <v>80</v>
       </c>
-      <c r="F37" s="6" t="s">
+      <c r="F37" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="6" t="s">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>110</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" t="s">
         <v>111</v>
       </c>
       <c r="C38">
         <v>1</v>
       </c>
-      <c r="D38" s="6" t="s">
+      <c r="D38" t="s">
         <v>63</v>
       </c>
-      <c r="E38" s="6" t="s">
+      <c r="E38" t="s">
         <v>80</v>
       </c>
       <c r="F38" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="6" t="s">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>113</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" t="s">
         <v>114</v>
       </c>
       <c r="C39">
         <v>2</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="D39" t="s">
         <v>67</v>
       </c>
-      <c r="E39" s="6" t="s">
+      <c r="E39" t="s">
         <v>80</v>
       </c>
-      <c r="F39" s="6" t="s">
+      <c r="F39" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="40" spans="2:6">
-      <c r="B40" s="6" t="s">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
         <v>116</v>
       </c>
       <c r="C40">
         <v>2</v>
       </c>
-      <c r="D40" s="6" t="s">
+      <c r="D40" t="s">
         <v>67</v>
       </c>
-      <c r="E40" s="6" t="s">
+      <c r="E40" t="s">
         <v>80</v>
       </c>
-      <c r="F40" s="6" t="s">
+      <c r="F40" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="41" ht="43.2" spans="2:6">
-      <c r="B41" s="6" t="s">
+    <row r="41" spans="1:6" ht="42" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
         <v>118</v>
       </c>
       <c r="C41">
         <v>2</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D41" t="s">
         <v>75</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="E41" t="s">
         <v>80</v>
       </c>
-      <c r="F41" s="7" t="s">
+      <c r="F41" s="2" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="8" t="s">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-    </row>
-    <row r="43" spans="1:6">
+      <c r="B42" s="11"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>28</v>
       </c>
@@ -2523,12 +1903,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
-      <c r="A44" t="s">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="B44" t="s">
         <v>121</v>
-      </c>
-      <c r="B44" t="s">
-        <v>122</v>
       </c>
       <c r="C44">
         <v>1</v>
@@ -2536,16 +1916,17 @@
       <c r="D44" t="s">
         <v>67</v>
       </c>
-      <c r="E44" t="s">
-        <v>80</v>
+      <c r="E44" s="14" t="s">
+        <v>144</v>
       </c>
       <c r="F44" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="12"/>
+      <c r="B45" t="s">
         <v>123</v>
-      </c>
-    </row>
-    <row r="45" spans="2:6">
-      <c r="B45" t="s">
-        <v>124</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -2553,16 +1934,17 @@
       <c r="D45" t="s">
         <v>67</v>
       </c>
-      <c r="E45" t="s">
-        <v>80</v>
+      <c r="E45" s="14" t="s">
+        <v>144</v>
       </c>
       <c r="F45" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="46" spans="2:6">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="13"/>
       <c r="B46" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -2570,19 +1952,19 @@
       <c r="D46" t="s">
         <v>67</v>
       </c>
-      <c r="E46" t="s">
-        <v>80</v>
+      <c r="E46" s="14" t="s">
+        <v>144</v>
       </c>
       <c r="F46" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47" t="s">
+      <c r="B47" t="s">
         <v>127</v>
-      </c>
-      <c r="B47" t="s">
-        <v>128</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -2594,15 +1976,15 @@
         <v>80</v>
       </c>
       <c r="F47" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48" t="s">
+      <c r="B48" t="s">
         <v>130</v>
-      </c>
-      <c r="B48" t="s">
-        <v>131</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -2614,15 +1996,15 @@
         <v>80</v>
       </c>
       <c r="F48" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49" t="s">
+      <c r="B49" t="s">
         <v>133</v>
-      </c>
-      <c r="B49" t="s">
-        <v>134</v>
       </c>
       <c r="C49">
         <v>1</v>
@@ -2634,15 +2016,15 @@
         <v>80</v>
       </c>
       <c r="F49" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>118</v>
       </c>
       <c r="B50" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C50">
         <v>2</v>
@@ -2654,15 +2036,15 @@
         <v>80</v>
       </c>
       <c r="F50" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51" t="s">
+      <c r="B51" t="s">
         <v>138</v>
-      </c>
-      <c r="B51" t="s">
-        <v>139</v>
       </c>
       <c r="C51">
         <v>4</v>
@@ -2674,79 +2056,79 @@
         <v>80</v>
       </c>
       <c r="F51" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="A44:A45"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="A27:F27"/>
     <mergeCell ref="A35:F35"/>
     <mergeCell ref="A42:F42"/>
   </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="5" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>143</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="2"/>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="2"/>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="2" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="8"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="8"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="2"/>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="2"/>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="2"/>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="8"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="8"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="A5:A8"/>
   </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>